--- a/outputs/Beans_(fava,_dry)_tukey_classification_matrix.xlsx
+++ b/outputs/Beans_(fava,_dry)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="115">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alarm</t>
@@ -976,10 +979,10 @@
         <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>103</v>
@@ -991,22 +994,22 @@
         <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I2" t="s">
         <v>103</v>
       </c>
       <c r="J2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N2" t="s">
         <v>103</v>
@@ -1018,7 +1021,7 @@
         <v>103</v>
       </c>
       <c r="Q2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R2" t="s">
         <v>103</v>
@@ -1036,7 +1039,7 @@
         <v>103</v>
       </c>
       <c r="W2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X2" t="s">
         <v>103</v>
@@ -1045,157 +1048,157 @@
         <v>103</v>
       </c>
       <c r="Z2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:76">
@@ -1203,154 +1206,154 @@
         <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ3" t="s">
         <v>103</v>
@@ -1359,73 +1362,73 @@
         <v>103</v>
       </c>
       <c r="BB3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ3" t="s">
         <v>103</v>
       </c>
       <c r="BR3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:76">
@@ -1439,7 +1442,7 @@
         <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>103</v>
@@ -1448,7 +1451,7 @@
         <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
         <v>103</v>
@@ -1472,16 +1475,16 @@
         <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P4" t="s">
         <v>103</v>
       </c>
       <c r="Q4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S4" t="s">
         <v>103</v>
@@ -1502,13 +1505,13 @@
         <v>103</v>
       </c>
       <c r="Y4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z4" t="s">
         <v>103</v>
       </c>
       <c r="AA4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB4" t="s">
         <v>103</v>
@@ -1520,7 +1523,7 @@
         <v>103</v>
       </c>
       <c r="AE4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF4" t="s">
         <v>103</v>
@@ -1532,10 +1535,10 @@
         <v>103</v>
       </c>
       <c r="AI4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s">
         <v>103</v>
@@ -1547,22 +1550,22 @@
         <v>103</v>
       </c>
       <c r="AN4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO4" t="s">
         <v>103</v>
       </c>
       <c r="AP4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ4" t="s">
         <v>103</v>
       </c>
       <c r="AR4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT4" t="s">
         <v>103</v>
@@ -1577,19 +1580,19 @@
         <v>103</v>
       </c>
       <c r="AX4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY4" t="s">
         <v>103</v>
       </c>
       <c r="AZ4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BA4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC4" t="s">
         <v>103</v>
@@ -1601,46 +1604,46 @@
         <v>103</v>
       </c>
       <c r="BF4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG4" t="s">
         <v>103</v>
       </c>
       <c r="BH4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN4" t="s">
         <v>105</v>
       </c>
-      <c r="BN4" t="s">
-        <v>104</v>
-      </c>
       <c r="BO4" t="s">
         <v>103</v>
       </c>
       <c r="BP4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BQ4" t="s">
         <v>103</v>
       </c>
       <c r="BR4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT4" t="s">
         <v>103</v>
@@ -1649,13 +1652,13 @@
         <v>103</v>
       </c>
       <c r="BV4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BW4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BX4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:76">
@@ -1663,55 +1666,55 @@
         <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S5" t="s">
         <v>103</v>
@@ -1723,7 +1726,7 @@
         <v>103</v>
       </c>
       <c r="V5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W5" t="s">
         <v>103</v>
@@ -1741,25 +1744,25 @@
         <v>103</v>
       </c>
       <c r="AB5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF5" t="s">
         <v>103</v>
       </c>
       <c r="AG5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI5" t="s">
         <v>103</v>
@@ -1768,7 +1771,7 @@
         <v>103</v>
       </c>
       <c r="AK5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s">
         <v>103</v>
@@ -1777,7 +1780,7 @@
         <v>103</v>
       </c>
       <c r="AN5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO5" t="s">
         <v>103</v>
@@ -1804,22 +1807,22 @@
         <v>103</v>
       </c>
       <c r="AW5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX5" t="s">
         <v>103</v>
       </c>
       <c r="AY5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC5" t="s">
         <v>103</v>
@@ -1846,7 +1849,7 @@
         <v>103</v>
       </c>
       <c r="BK5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL5" t="s">
         <v>103</v>
@@ -1873,19 +1876,19 @@
         <v>103</v>
       </c>
       <c r="BT5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:76">
@@ -1893,55 +1896,55 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S6" t="s">
         <v>103</v>
@@ -1950,10 +1953,10 @@
         <v>103</v>
       </c>
       <c r="U6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W6" t="s">
         <v>103</v>
@@ -1962,19 +1965,19 @@
         <v>103</v>
       </c>
       <c r="Y6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD6" t="s">
         <v>103</v>
@@ -1983,28 +1986,28 @@
         <v>103</v>
       </c>
       <c r="AF6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s">
         <v>103</v>
       </c>
       <c r="AH6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI6" t="s">
         <v>103</v>
       </c>
       <c r="AJ6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s">
         <v>103</v>
       </c>
       <c r="AL6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN6" t="s">
         <v>103</v>
@@ -2028,7 +2031,7 @@
         <v>103</v>
       </c>
       <c r="AU6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV6" t="s">
         <v>103</v>
@@ -2061,7 +2064,7 @@
         <v>103</v>
       </c>
       <c r="BF6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG6" t="s">
         <v>103</v>
@@ -2073,49 +2076,49 @@
         <v>103</v>
       </c>
       <c r="BJ6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:76">
@@ -2123,202 +2126,202 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP7" t="s">
         <v>103</v>
@@ -2327,25 +2330,25 @@
         <v>103</v>
       </c>
       <c r="BR7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:76">
@@ -2353,55 +2356,55 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S8" t="s">
         <v>103</v>
@@ -2413,7 +2416,7 @@
         <v>103</v>
       </c>
       <c r="V8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W8" t="s">
         <v>103</v>
@@ -2425,7 +2428,7 @@
         <v>103</v>
       </c>
       <c r="Z8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA8" t="s">
         <v>103</v>
@@ -2440,7 +2443,7 @@
         <v>103</v>
       </c>
       <c r="AE8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF8" t="s">
         <v>103</v>
@@ -2458,7 +2461,7 @@
         <v>103</v>
       </c>
       <c r="AK8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL8" t="s">
         <v>103</v>
@@ -2467,55 +2470,55 @@
         <v>103</v>
       </c>
       <c r="AN8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO8" t="s">
         <v>103</v>
       </c>
       <c r="AP8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR8" t="s">
         <v>103</v>
       </c>
       <c r="AS8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ8" t="s">
         <v>103</v>
       </c>
       <c r="BA8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC8" t="s">
         <v>103</v>
       </c>
       <c r="BD8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE8" t="s">
         <v>103</v>
@@ -2524,58 +2527,58 @@
         <v>103</v>
       </c>
       <c r="BG8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ8" t="s">
         <v>103</v>
       </c>
       <c r="BK8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:76">
@@ -2583,28 +2586,28 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H9" t="s">
         <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J9" t="s">
         <v>103</v>
@@ -2625,16 +2628,16 @@
         <v>103</v>
       </c>
       <c r="P9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q9" t="s">
         <v>103</v>
       </c>
       <c r="R9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T9" t="s">
         <v>103</v>
@@ -2646,16 +2649,16 @@
         <v>103</v>
       </c>
       <c r="W9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y9" t="s">
         <v>103</v>
       </c>
       <c r="Z9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA9" t="s">
         <v>103</v>
@@ -2664,148 +2667,148 @@
         <v>103</v>
       </c>
       <c r="AC9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:76">
@@ -2813,106 +2816,106 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ10" t="s">
         <v>103</v>
@@ -2924,7 +2927,7 @@
         <v>103</v>
       </c>
       <c r="AM10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN10" t="s">
         <v>103</v>
@@ -2948,7 +2951,7 @@
         <v>103</v>
       </c>
       <c r="AU10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV10" t="s">
         <v>103</v>
@@ -2960,67 +2963,67 @@
         <v>103</v>
       </c>
       <c r="AY10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ10" t="s">
         <v>103</v>
       </c>
       <c r="BR10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT10" t="s">
         <v>103</v>
@@ -3029,13 +3032,13 @@
         <v>103</v>
       </c>
       <c r="BV10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:76">
@@ -3043,205 +3046,205 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ11" t="s">
         <v>103</v>
@@ -3250,22 +3253,22 @@
         <v>103</v>
       </c>
       <c r="BS11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:76">
@@ -3273,229 +3276,229 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV12" t="s">
         <v>103</v>
       </c>
       <c r="AW12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB12" t="s">
         <v>103</v>
       </c>
       <c r="BC12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO12" t="s">
         <v>103</v>
       </c>
       <c r="BP12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:76">
@@ -3503,7 +3506,7 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
         <v>103</v>
@@ -3515,7 +3518,7 @@
         <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
         <v>103</v>
@@ -3530,13 +3533,13 @@
         <v>103</v>
       </c>
       <c r="K13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s">
         <v>103</v>
       </c>
       <c r="M13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N13" t="s">
         <v>103</v>
@@ -3554,7 +3557,7 @@
         <v>103</v>
       </c>
       <c r="S13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T13" t="s">
         <v>103</v>
@@ -3566,19 +3569,19 @@
         <v>103</v>
       </c>
       <c r="W13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X13" t="s">
         <v>103</v>
       </c>
       <c r="Y13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z13" t="s">
         <v>103</v>
       </c>
       <c r="AA13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB13" t="s">
         <v>103</v>
@@ -3587,7 +3590,7 @@
         <v>103</v>
       </c>
       <c r="AD13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE13" t="s">
         <v>103</v>
@@ -3599,13 +3602,13 @@
         <v>103</v>
       </c>
       <c r="AH13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s">
         <v>103</v>
@@ -3629,10 +3632,10 @@
         <v>103</v>
       </c>
       <c r="AR13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT13" t="s">
         <v>103</v>
@@ -3656,7 +3659,7 @@
         <v>103</v>
       </c>
       <c r="BA13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB13" t="s">
         <v>103</v>
@@ -3665,7 +3668,7 @@
         <v>103</v>
       </c>
       <c r="BD13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE13" t="s">
         <v>103</v>
@@ -3674,58 +3677,58 @@
         <v>103</v>
       </c>
       <c r="BG13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BI13" t="s">
         <v>103</v>
       </c>
       <c r="BJ13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BK13" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL13" t="s">
         <v>105</v>
       </c>
-      <c r="BL13" t="s">
-        <v>104</v>
-      </c>
       <c r="BM13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BN13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO13" t="s">
         <v>103</v>
       </c>
       <c r="BP13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BR13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BS13" t="s">
         <v>103</v>
       </c>
       <c r="BT13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV13" t="s">
+        <v>109</v>
+      </c>
+      <c r="BW13" t="s">
         <v>108</v>
       </c>
-      <c r="BW13" t="s">
-        <v>107</v>
-      </c>
       <c r="BX13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:76">
@@ -3745,28 +3748,28 @@
         <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
         <v>103</v>
       </c>
       <c r="I14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J14" t="s">
         <v>103</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s">
         <v>103</v>
       </c>
       <c r="M14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N14" t="s">
         <v>103</v>
@@ -3775,7 +3778,7 @@
         <v>103</v>
       </c>
       <c r="P14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q14" t="s">
         <v>103</v>
@@ -3793,7 +3796,7 @@
         <v>103</v>
       </c>
       <c r="V14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W14" t="s">
         <v>103</v>
@@ -3802,19 +3805,19 @@
         <v>103</v>
       </c>
       <c r="Y14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB14" t="s">
         <v>103</v>
       </c>
       <c r="AC14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD14" t="s">
         <v>103</v>
@@ -3826,7 +3829,7 @@
         <v>103</v>
       </c>
       <c r="AG14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH14" t="s">
         <v>103</v>
@@ -3835,19 +3838,19 @@
         <v>103</v>
       </c>
       <c r="AJ14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
       <c r="AL14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM14" t="s">
         <v>103</v>
       </c>
       <c r="AN14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO14" t="s">
         <v>103</v>
@@ -3859,10 +3862,10 @@
         <v>103</v>
       </c>
       <c r="AR14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT14" t="s">
         <v>103</v>
@@ -3904,7 +3907,7 @@
         <v>103</v>
       </c>
       <c r="BG14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH14" t="s">
         <v>103</v>
@@ -3928,7 +3931,7 @@
         <v>103</v>
       </c>
       <c r="BO14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BP14" t="s">
         <v>103</v>
@@ -3949,13 +3952,13 @@
         <v>103</v>
       </c>
       <c r="BV14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:76">
@@ -3963,7 +3966,7 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
@@ -3972,19 +3975,19 @@
         <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" t="s">
         <v>103</v>
       </c>
       <c r="H15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J15" t="s">
         <v>103</v>
@@ -3999,19 +4002,19 @@
         <v>103</v>
       </c>
       <c r="N15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S15" t="s">
         <v>103</v>
@@ -4020,52 +4023,52 @@
         <v>103</v>
       </c>
       <c r="U15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s">
         <v>103</v>
@@ -4074,64 +4077,64 @@
         <v>103</v>
       </c>
       <c r="AM15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP15" t="s">
         <v>103</v>
       </c>
       <c r="AQ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR15" t="s">
         <v>103</v>
       </c>
       <c r="AS15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW15" t="s">
         <v>103</v>
       </c>
       <c r="AX15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY15" t="s">
         <v>103</v>
       </c>
       <c r="AZ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD15" t="s">
         <v>103</v>
       </c>
       <c r="BE15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG15" t="s">
         <v>103</v>
@@ -4140,25 +4143,25 @@
         <v>103</v>
       </c>
       <c r="BI15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL15" t="s">
         <v>103</v>
       </c>
       <c r="BM15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN15" t="s">
         <v>103</v>
       </c>
       <c r="BO15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP15" t="s">
         <v>103</v>
@@ -4167,25 +4170,25 @@
         <v>103</v>
       </c>
       <c r="BR15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT15" t="s">
         <v>103</v>
       </c>
       <c r="BU15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:76">
@@ -4196,7 +4199,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -4208,7 +4211,7 @@
         <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
         <v>103</v>
@@ -4217,7 +4220,7 @@
         <v>103</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K16" t="s">
         <v>103</v>
@@ -4226,10 +4229,10 @@
         <v>103</v>
       </c>
       <c r="M16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O16" t="s">
         <v>103</v>
@@ -4238,19 +4241,19 @@
         <v>103</v>
       </c>
       <c r="Q16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V16" t="s">
         <v>103</v>
@@ -4274,10 +4277,10 @@
         <v>103</v>
       </c>
       <c r="AC16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE16" t="s">
         <v>103</v>
@@ -4298,7 +4301,7 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL16" t="s">
         <v>103</v>
@@ -4310,10 +4313,10 @@
         <v>103</v>
       </c>
       <c r="AO16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ16" t="s">
         <v>103</v>
@@ -4322,10 +4325,10 @@
         <v>103</v>
       </c>
       <c r="AS16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU16" t="s">
         <v>103</v>
@@ -4334,22 +4337,22 @@
         <v>103</v>
       </c>
       <c r="AW16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX16" t="s">
         <v>103</v>
       </c>
       <c r="AY16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC16" t="s">
         <v>103</v>
@@ -4367,13 +4370,13 @@
         <v>103</v>
       </c>
       <c r="BH16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI16" t="s">
         <v>103</v>
       </c>
       <c r="BJ16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK16" t="s">
         <v>103</v>
@@ -4382,40 +4385,40 @@
         <v>103</v>
       </c>
       <c r="BM16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO16" t="s">
         <v>103</v>
       </c>
       <c r="BP16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ16" t="s">
         <v>103</v>
       </c>
       <c r="BR16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS16" t="s">
         <v>103</v>
       </c>
       <c r="BT16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:76">
@@ -4423,16 +4426,16 @@
         <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
         <v>103</v>
@@ -4444,40 +4447,40 @@
         <v>103</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N17" t="s">
         <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q17" t="s">
         <v>103</v>
       </c>
       <c r="R17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
@@ -4492,16 +4495,16 @@
         <v>103</v>
       </c>
       <c r="Y17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC17" t="s">
         <v>103</v>
@@ -4510,22 +4513,22 @@
         <v>103</v>
       </c>
       <c r="AE17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG17" t="s">
         <v>103</v>
       </c>
       <c r="AH17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI17" t="s">
         <v>103</v>
       </c>
       <c r="AJ17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK17" t="s">
         <v>103</v>
@@ -4534,25 +4537,25 @@
         <v>103</v>
       </c>
       <c r="AM17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR17" t="s">
         <v>103</v>
       </c>
       <c r="AS17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT17" t="s">
         <v>103</v>
@@ -4561,31 +4564,31 @@
         <v>103</v>
       </c>
       <c r="AV17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX17" t="s">
         <v>103</v>
       </c>
       <c r="AY17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC17" t="s">
         <v>103</v>
       </c>
       <c r="BD17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE17" t="s">
         <v>103</v>
@@ -4597,7 +4600,7 @@
         <v>103</v>
       </c>
       <c r="BH17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI17" t="s">
         <v>103</v>
@@ -4606,28 +4609,28 @@
         <v>103</v>
       </c>
       <c r="BK17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL17" t="s">
         <v>103</v>
       </c>
       <c r="BM17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BN17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO17" t="s">
         <v>103</v>
       </c>
       <c r="BP17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ17" t="s">
         <v>103</v>
       </c>
       <c r="BR17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS17" t="s">
         <v>103</v>
@@ -4636,16 +4639,16 @@
         <v>103</v>
       </c>
       <c r="BU17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:76">
@@ -4656,7 +4659,7 @@
         <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -4674,25 +4677,25 @@
         <v>103</v>
       </c>
       <c r="I18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M18" t="s">
         <v>103</v>
       </c>
       <c r="N18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P18" t="s">
         <v>103</v>
@@ -4701,7 +4704,7 @@
         <v>103</v>
       </c>
       <c r="R18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S18" t="s">
         <v>103</v>
@@ -4710,7 +4713,7 @@
         <v>103</v>
       </c>
       <c r="U18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V18" t="s">
         <v>103</v>
@@ -4734,22 +4737,22 @@
         <v>103</v>
       </c>
       <c r="AC18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF18" t="s">
         <v>103</v>
       </c>
       <c r="AG18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI18" t="s">
         <v>103</v>
@@ -4758,124 +4761,124 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL18" t="s">
         <v>103</v>
       </c>
       <c r="AM18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP18" t="s">
         <v>103</v>
       </c>
       <c r="AQ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD18" t="s">
         <v>103</v>
       </c>
       <c r="BE18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:76">
@@ -4883,7 +4886,7 @@
         <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
@@ -4892,7 +4895,7 @@
         <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
         <v>103</v>
@@ -4904,16 +4907,16 @@
         <v>103</v>
       </c>
       <c r="I19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M19" t="s">
         <v>103</v>
@@ -4925,52 +4928,52 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R19" t="s">
         <v>103</v>
       </c>
       <c r="S19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V19" t="s">
         <v>103</v>
       </c>
       <c r="W19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X19" t="s">
         <v>103</v>
       </c>
       <c r="Y19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z19" t="s">
         <v>103</v>
       </c>
       <c r="AA19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC19" t="s">
         <v>103</v>
       </c>
       <c r="AD19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF19" t="s">
         <v>103</v>
@@ -4982,49 +4985,49 @@
         <v>103</v>
       </c>
       <c r="AI19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s">
         <v>103</v>
       </c>
       <c r="AL19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO19" t="s">
         <v>103</v>
       </c>
       <c r="AP19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ19" t="s">
         <v>103</v>
       </c>
       <c r="AR19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS19" t="s">
         <v>103</v>
       </c>
       <c r="AT19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV19" t="s">
         <v>103</v>
       </c>
       <c r="AW19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX19" t="s">
         <v>103</v>
@@ -5036,10 +5039,10 @@
         <v>103</v>
       </c>
       <c r="BA19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC19" t="s">
         <v>103</v>
@@ -5057,7 +5060,7 @@
         <v>103</v>
       </c>
       <c r="BH19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI19" t="s">
         <v>103</v>
@@ -5075,7 +5078,7 @@
         <v>103</v>
       </c>
       <c r="BN19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BO19" t="s">
         <v>103</v>
@@ -5093,19 +5096,19 @@
         <v>103</v>
       </c>
       <c r="BT19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:76">
@@ -5113,142 +5116,142 @@
         <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV20" t="s">
         <v>103</v>
@@ -5260,22 +5263,22 @@
         <v>103</v>
       </c>
       <c r="AY20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ20" t="s">
         <v>103</v>
       </c>
       <c r="BA20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC20" t="s">
         <v>103</v>
       </c>
       <c r="BD20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE20" t="s">
         <v>103</v>
@@ -5287,16 +5290,16 @@
         <v>103</v>
       </c>
       <c r="BH20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI20" t="s">
         <v>103</v>
       </c>
       <c r="BJ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL20" t="s">
         <v>103</v>
@@ -5305,37 +5308,37 @@
         <v>103</v>
       </c>
       <c r="BN20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR20" t="s">
         <v>103</v>
       </c>
       <c r="BS20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:76">
@@ -5343,13 +5346,13 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>103</v>
@@ -5358,61 +5361,61 @@
         <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H21" t="s">
         <v>103</v>
       </c>
       <c r="I21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z21" t="s">
         <v>103</v>
@@ -5424,10 +5427,10 @@
         <v>103</v>
       </c>
       <c r="AC21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE21" t="s">
         <v>103</v>
@@ -5469,19 +5472,19 @@
         <v>103</v>
       </c>
       <c r="AR21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT21" t="s">
         <v>103</v>
       </c>
       <c r="AU21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW21" t="s">
         <v>103</v>
@@ -5490,49 +5493,49 @@
         <v>103</v>
       </c>
       <c r="AY21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC21" t="s">
         <v>103</v>
       </c>
       <c r="BD21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG21" t="s">
         <v>103</v>
       </c>
       <c r="BH21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL21" t="s">
         <v>103</v>
       </c>
       <c r="BM21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN21" t="s">
         <v>103</v>
@@ -5541,7 +5544,7 @@
         <v>103</v>
       </c>
       <c r="BP21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ21" t="s">
         <v>103</v>
@@ -5550,22 +5553,22 @@
         <v>103</v>
       </c>
       <c r="BS21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:76">
@@ -5573,13 +5576,13 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
         <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>103</v>
@@ -5591,22 +5594,22 @@
         <v>103</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N22" t="s">
         <v>103</v>
@@ -5615,7 +5618,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q22" t="s">
         <v>103</v>
@@ -5630,13 +5633,13 @@
         <v>103</v>
       </c>
       <c r="U22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V22" t="s">
         <v>103</v>
       </c>
       <c r="W22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X22" t="s">
         <v>103</v>
@@ -5666,7 +5669,7 @@
         <v>103</v>
       </c>
       <c r="AG22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH22" t="s">
         <v>103</v>
@@ -5675,13 +5678,13 @@
         <v>103</v>
       </c>
       <c r="AJ22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s">
         <v>103</v>
       </c>
       <c r="AL22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM22" t="s">
         <v>103</v>
@@ -5693,7 +5696,7 @@
         <v>103</v>
       </c>
       <c r="AP22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ22" t="s">
         <v>103</v>
@@ -5711,7 +5714,7 @@
         <v>103</v>
       </c>
       <c r="AV22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW22" t="s">
         <v>103</v>
@@ -5726,22 +5729,22 @@
         <v>103</v>
       </c>
       <c r="BA22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BC22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD22" t="s">
         <v>103</v>
       </c>
       <c r="BE22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG22" t="s">
         <v>103</v>
@@ -5762,13 +5765,13 @@
         <v>103</v>
       </c>
       <c r="BM22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BN22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP22" t="s">
         <v>103</v>
@@ -5789,13 +5792,13 @@
         <v>103</v>
       </c>
       <c r="BV22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BX22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:76">
@@ -5803,46 +5806,46 @@
         <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
         <v>103</v>
       </c>
       <c r="K23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P23" t="s">
         <v>103</v>
@@ -5851,10 +5854,10 @@
         <v>103</v>
       </c>
       <c r="R23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T23" t="s">
         <v>103</v>
@@ -5863,13 +5866,13 @@
         <v>103</v>
       </c>
       <c r="V23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y23" t="s">
         <v>103</v>
@@ -5878,13 +5881,13 @@
         <v>103</v>
       </c>
       <c r="AA23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB23" t="s">
         <v>103</v>
       </c>
       <c r="AC23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD23" t="s">
         <v>103</v>
@@ -5896,7 +5899,7 @@
         <v>103</v>
       </c>
       <c r="AG23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH23" t="s">
         <v>103</v>
@@ -5905,19 +5908,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s">
         <v>103</v>
       </c>
       <c r="AL23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO23" t="s">
         <v>103</v>
@@ -5926,70 +5929,70 @@
         <v>103</v>
       </c>
       <c r="AQ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR23" t="s">
         <v>103</v>
       </c>
       <c r="AS23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT23" t="s">
         <v>103</v>
       </c>
       <c r="AU23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC23" t="s">
         <v>103</v>
       </c>
       <c r="BD23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF23" t="s">
         <v>103</v>
       </c>
       <c r="BG23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM23" t="s">
         <v>103</v>
@@ -5998,16 +6001,16 @@
         <v>103</v>
       </c>
       <c r="BO23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS23" t="s">
         <v>103</v>
@@ -6016,16 +6019,16 @@
         <v>103</v>
       </c>
       <c r="BU23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:76">
@@ -6033,151 +6036,151 @@
         <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY24" t="s">
         <v>103</v>
@@ -6192,34 +6195,34 @@
         <v>103</v>
       </c>
       <c r="BC24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD24" t="s">
         <v>103</v>
       </c>
       <c r="BE24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF24" t="s">
         <v>103</v>
       </c>
       <c r="BG24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI24" t="s">
         <v>103</v>
       </c>
       <c r="BJ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK24" t="s">
         <v>103</v>
       </c>
       <c r="BL24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM24" t="s">
         <v>103</v>
@@ -6234,7 +6237,7 @@
         <v>103</v>
       </c>
       <c r="BQ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR24" t="s">
         <v>103</v>
@@ -6243,19 +6246,19 @@
         <v>103</v>
       </c>
       <c r="BT24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:76">
@@ -6263,136 +6266,136 @@
         <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL25" t="s">
         <v>103</v>
       </c>
       <c r="AM25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP25" t="s">
         <v>103</v>
       </c>
       <c r="AQ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT25" t="s">
         <v>103</v>
@@ -6404,43 +6407,43 @@
         <v>103</v>
       </c>
       <c r="AW25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ25" t="s">
         <v>103</v>
@@ -6449,10 +6452,10 @@
         <v>103</v>
       </c>
       <c r="BL25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN25" t="s">
         <v>103</v>
@@ -6461,31 +6464,31 @@
         <v>103</v>
       </c>
       <c r="BP25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT25" t="s">
         <v>103</v>
       </c>
       <c r="BU25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:76">
@@ -6493,91 +6496,91 @@
         <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC26" t="s">
         <v>103</v>
       </c>
       <c r="AD26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE26" t="s">
         <v>103</v>
@@ -6589,55 +6592,55 @@
         <v>103</v>
       </c>
       <c r="AH26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN26" t="s">
         <v>103</v>
       </c>
       <c r="AO26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ26" t="s">
         <v>103</v>
       </c>
       <c r="AR26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY26" t="s">
         <v>103</v>
@@ -6652,25 +6655,25 @@
         <v>103</v>
       </c>
       <c r="BC26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ26" t="s">
         <v>103</v>
@@ -6700,22 +6703,22 @@
         <v>103</v>
       </c>
       <c r="BS26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:76">
@@ -6723,7 +6726,7 @@
         <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
         <v>103</v>
@@ -6732,10 +6735,10 @@
         <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G27" t="s">
         <v>103</v>
@@ -6744,64 +6747,64 @@
         <v>103</v>
       </c>
       <c r="I27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
         <v>103</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s">
         <v>103</v>
       </c>
       <c r="M27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" t="s">
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U27" t="s">
         <v>103</v>
       </c>
       <c r="V27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X27" t="s">
         <v>103</v>
       </c>
       <c r="Y27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z27" t="s">
         <v>103</v>
       </c>
       <c r="AA27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC27" t="s">
         <v>103</v>
@@ -6813,91 +6816,91 @@
         <v>103</v>
       </c>
       <c r="AF27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG27" t="s">
         <v>103</v>
       </c>
       <c r="AH27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI27" t="s">
         <v>103</v>
       </c>
       <c r="AJ27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s">
         <v>103</v>
       </c>
       <c r="AL27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM27" t="s">
         <v>103</v>
       </c>
       <c r="AN27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR27" t="s">
         <v>103</v>
       </c>
       <c r="AS27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU27" t="s">
         <v>103</v>
       </c>
       <c r="AV27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX27" t="s">
         <v>103</v>
       </c>
       <c r="AY27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ27" t="s">
         <v>103</v>
       </c>
       <c r="BA27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD27" t="s">
         <v>103</v>
       </c>
       <c r="BE27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BI27" t="s">
         <v>103</v>
@@ -6906,46 +6909,46 @@
         <v>103</v>
       </c>
       <c r="BK27" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL27" t="s">
+        <v>103</v>
+      </c>
+      <c r="BM27" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN27" t="s">
+        <v>103</v>
+      </c>
+      <c r="BO27" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP27" t="s">
+        <v>104</v>
+      </c>
+      <c r="BQ27" t="s">
         <v>105</v>
       </c>
-      <c r="BL27" t="s">
-        <v>103</v>
-      </c>
-      <c r="BM27" t="s">
-        <v>103</v>
-      </c>
-      <c r="BN27" t="s">
-        <v>103</v>
-      </c>
-      <c r="BO27" t="s">
-        <v>103</v>
-      </c>
-      <c r="BP27" t="s">
-        <v>103</v>
-      </c>
-      <c r="BQ27" t="s">
-        <v>104</v>
-      </c>
       <c r="BR27" t="s">
         <v>103</v>
       </c>
       <c r="BS27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BW27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:76">
@@ -6953,43 +6956,43 @@
         <v>102</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" t="s">
         <v>103</v>
@@ -7016,7 +7019,7 @@
         <v>103</v>
       </c>
       <c r="W28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X28" t="s">
         <v>103</v>
@@ -7067,115 +7070,115 @@
         <v>103</v>
       </c>
       <c r="AN28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BM28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BN28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BO28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BP28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BU28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BV28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Beans_(fava,_dry)_tukey_classification_matrix.xlsx
+++ b/outputs/Beans_(fava,_dry)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="106">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -331,34 +331,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>8%</t>
   </si>
 </sst>
 </file>
@@ -985,7 +958,7 @@
         <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
         <v>103</v>
@@ -1015,10 +988,10 @@
         <v>103</v>
       </c>
       <c r="O2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="s">
         <v>104</v>
@@ -1030,22 +1003,22 @@
         <v>103</v>
       </c>
       <c r="T2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U2" t="s">
         <v>103</v>
       </c>
       <c r="V2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W2" t="s">
         <v>104</v>
       </c>
       <c r="X2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z2" t="s">
         <v>104</v>
@@ -1192,13 +1165,13 @@
         <v>104</v>
       </c>
       <c r="BV2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:76">
@@ -1356,10 +1329,10 @@
         <v>104</v>
       </c>
       <c r="AZ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB3" t="s">
         <v>104</v>
@@ -1407,7 +1380,7 @@
         <v>104</v>
       </c>
       <c r="BQ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR3" t="s">
         <v>104</v>
@@ -1422,13 +1395,13 @@
         <v>104</v>
       </c>
       <c r="BV3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:76">
@@ -1586,7 +1559,7 @@
         <v>103</v>
       </c>
       <c r="AZ4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BA4" t="s">
         <v>104</v>
@@ -1625,16 +1598,16 @@
         <v>104</v>
       </c>
       <c r="BM4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BO4" t="s">
         <v>103</v>
       </c>
       <c r="BP4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BQ4" t="s">
         <v>103</v>
@@ -1652,13 +1625,13 @@
         <v>103</v>
       </c>
       <c r="BV4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BW4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BX4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:76">
@@ -1852,7 +1825,7 @@
         <v>104</v>
       </c>
       <c r="BL5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM5" t="s">
         <v>103</v>
@@ -1882,13 +1855,13 @@
         <v>104</v>
       </c>
       <c r="BV5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:76">
@@ -2028,7 +2001,7 @@
         <v>103</v>
       </c>
       <c r="AT6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU6" t="s">
         <v>104</v>
@@ -2040,10 +2013,10 @@
         <v>103</v>
       </c>
       <c r="AX6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ6" t="s">
         <v>103</v>
@@ -2112,13 +2085,13 @@
         <v>104</v>
       </c>
       <c r="BV6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:76">
@@ -2324,10 +2297,10 @@
         <v>104</v>
       </c>
       <c r="BP7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR7" t="s">
         <v>104</v>
@@ -2342,13 +2315,13 @@
         <v>104</v>
       </c>
       <c r="BV7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:76">
@@ -2425,7 +2398,7 @@
         <v>103</v>
       </c>
       <c r="Y8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z8" t="s">
         <v>104</v>
@@ -2440,7 +2413,7 @@
         <v>103</v>
       </c>
       <c r="AD8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE8" t="s">
         <v>104</v>
@@ -2572,13 +2545,13 @@
         <v>104</v>
       </c>
       <c r="BV8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:76">
@@ -2613,16 +2586,16 @@
         <v>103</v>
       </c>
       <c r="K9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s">
         <v>103</v>
       </c>
       <c r="N9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O9" t="s">
         <v>103</v>
@@ -2631,7 +2604,7 @@
         <v>104</v>
       </c>
       <c r="Q9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R9" t="s">
         <v>104</v>
@@ -2643,7 +2616,7 @@
         <v>103</v>
       </c>
       <c r="U9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V9" t="s">
         <v>103</v>
@@ -2664,7 +2637,7 @@
         <v>103</v>
       </c>
       <c r="AB9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC9" t="s">
         <v>104</v>
@@ -2802,13 +2775,13 @@
         <v>104</v>
       </c>
       <c r="BV9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:76">
@@ -2930,25 +2903,25 @@
         <v>104</v>
       </c>
       <c r="AN10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS10" t="s">
         <v>103</v>
       </c>
       <c r="AT10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU10" t="s">
         <v>104</v>
@@ -3032,13 +3005,13 @@
         <v>103</v>
       </c>
       <c r="BV10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:76">
@@ -3247,10 +3220,10 @@
         <v>104</v>
       </c>
       <c r="BQ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS11" t="s">
         <v>104</v>
@@ -3262,13 +3235,13 @@
         <v>104</v>
       </c>
       <c r="BV11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:76">
@@ -3414,7 +3387,7 @@
         <v>104</v>
       </c>
       <c r="AV12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW12" t="s">
         <v>104</v>
@@ -3432,7 +3405,7 @@
         <v>104</v>
       </c>
       <c r="BB12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC12" t="s">
         <v>104</v>
@@ -3471,7 +3444,7 @@
         <v>104</v>
       </c>
       <c r="BO12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP12" t="s">
         <v>104</v>
@@ -3492,13 +3465,13 @@
         <v>104</v>
       </c>
       <c r="BV12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:76">
@@ -3680,22 +3653,22 @@
         <v>104</v>
       </c>
       <c r="BH13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BI13" t="s">
         <v>103</v>
       </c>
       <c r="BJ13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BK13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BN13" t="s">
         <v>104</v>
@@ -3707,10 +3680,10 @@
         <v>104</v>
       </c>
       <c r="BQ13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BR13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BS13" t="s">
         <v>103</v>
@@ -3722,13 +3695,13 @@
         <v>104</v>
       </c>
       <c r="BV13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BW13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BX13" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:76">
@@ -3931,7 +3904,7 @@
         <v>103</v>
       </c>
       <c r="BO14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BP14" t="s">
         <v>103</v>
@@ -3952,13 +3925,13 @@
         <v>103</v>
       </c>
       <c r="BV14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW14" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX14" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:76">
@@ -3990,7 +3963,7 @@
         <v>104</v>
       </c>
       <c r="J15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
         <v>103</v>
@@ -4074,7 +4047,7 @@
         <v>103</v>
       </c>
       <c r="AL15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM15" t="s">
         <v>104</v>
@@ -4167,7 +4140,7 @@
         <v>103</v>
       </c>
       <c r="BQ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR15" t="s">
         <v>104</v>
@@ -4182,13 +4155,13 @@
         <v>104</v>
       </c>
       <c r="BV15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:76">
@@ -4205,10 +4178,10 @@
         <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" t="s">
         <v>104</v>
@@ -4412,13 +4385,13 @@
         <v>104</v>
       </c>
       <c r="BV16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:76">
@@ -4612,10 +4585,10 @@
         <v>104</v>
       </c>
       <c r="BL17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BN17" t="s">
         <v>104</v>
@@ -4642,13 +4615,13 @@
         <v>104</v>
       </c>
       <c r="BV17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BW17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:76">
@@ -4716,7 +4689,7 @@
         <v>104</v>
       </c>
       <c r="V18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W18" t="s">
         <v>103</v>
@@ -4731,7 +4704,7 @@
         <v>103</v>
       </c>
       <c r="AA18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB18" t="s">
         <v>103</v>
@@ -4872,13 +4845,13 @@
         <v>104</v>
       </c>
       <c r="BV18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:76">
@@ -5078,7 +5051,7 @@
         <v>103</v>
       </c>
       <c r="BN19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BO19" t="s">
         <v>103</v>
@@ -5102,13 +5075,13 @@
         <v>104</v>
       </c>
       <c r="BV19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:76">
@@ -5254,13 +5227,13 @@
         <v>104</v>
       </c>
       <c r="AV20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW20" t="s">
         <v>103</v>
       </c>
       <c r="AX20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY20" t="s">
         <v>104</v>
@@ -5275,19 +5248,19 @@
         <v>104</v>
       </c>
       <c r="BC20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD20" t="s">
         <v>104</v>
       </c>
       <c r="BE20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF20" t="s">
         <v>103</v>
       </c>
       <c r="BG20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH20" t="s">
         <v>104</v>
@@ -5305,7 +5278,7 @@
         <v>103</v>
       </c>
       <c r="BM20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN20" t="s">
         <v>104</v>
@@ -5332,13 +5305,13 @@
         <v>104</v>
       </c>
       <c r="BV20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:76">
@@ -5448,7 +5421,7 @@
         <v>103</v>
       </c>
       <c r="AJ21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s">
         <v>103</v>
@@ -5562,13 +5535,13 @@
         <v>104</v>
       </c>
       <c r="BV21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:76">
@@ -5732,7 +5705,7 @@
         <v>104</v>
       </c>
       <c r="BB22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BC22" t="s">
         <v>104</v>
@@ -5765,7 +5738,7 @@
         <v>103</v>
       </c>
       <c r="BM22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN22" t="s">
         <v>104</v>
@@ -5792,13 +5765,13 @@
         <v>103</v>
       </c>
       <c r="BV22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BX22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:76">
@@ -5863,7 +5836,7 @@
         <v>103</v>
       </c>
       <c r="U23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V23" t="s">
         <v>104</v>
@@ -5878,7 +5851,7 @@
         <v>103</v>
       </c>
       <c r="Z23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA23" t="s">
         <v>104</v>
@@ -6016,19 +5989,19 @@
         <v>103</v>
       </c>
       <c r="BT23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU23" t="s">
         <v>104</v>
       </c>
       <c r="BV23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:76">
@@ -6186,7 +6159,7 @@
         <v>103</v>
       </c>
       <c r="AZ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA24" t="s">
         <v>103</v>
@@ -6213,7 +6186,7 @@
         <v>104</v>
       </c>
       <c r="BI24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ24" t="s">
         <v>104</v>
@@ -6231,7 +6204,7 @@
         <v>103</v>
       </c>
       <c r="BO24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP24" t="s">
         <v>103</v>
@@ -6243,7 +6216,7 @@
         <v>103</v>
       </c>
       <c r="BS24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT24" t="s">
         <v>104</v>
@@ -6252,13 +6225,13 @@
         <v>104</v>
       </c>
       <c r="BV24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:76">
@@ -6398,10 +6371,10 @@
         <v>104</v>
       </c>
       <c r="AT25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV25" t="s">
         <v>103</v>
@@ -6449,7 +6422,7 @@
         <v>103</v>
       </c>
       <c r="BK25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL25" t="s">
         <v>104</v>
@@ -6461,7 +6434,7 @@
         <v>103</v>
       </c>
       <c r="BO25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP25" t="s">
         <v>104</v>
@@ -6482,13 +6455,13 @@
         <v>104</v>
       </c>
       <c r="BV25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:76">
@@ -6676,7 +6649,7 @@
         <v>104</v>
       </c>
       <c r="BJ26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK26" t="s">
         <v>103</v>
@@ -6700,7 +6673,7 @@
         <v>103</v>
       </c>
       <c r="BR26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS26" t="s">
         <v>104</v>
@@ -6712,13 +6685,13 @@
         <v>104</v>
       </c>
       <c r="BV26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:76">
@@ -6900,7 +6873,7 @@
         <v>104</v>
       </c>
       <c r="BH27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BI27" t="s">
         <v>103</v>
@@ -6909,7 +6882,7 @@
         <v>103</v>
       </c>
       <c r="BK27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL27" t="s">
         <v>103</v>
@@ -6927,7 +6900,7 @@
         <v>104</v>
       </c>
       <c r="BQ27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BR27" t="s">
         <v>103</v>
@@ -6942,13 +6915,13 @@
         <v>104</v>
       </c>
       <c r="BV27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BW27" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:76">
@@ -7055,7 +7028,7 @@
         <v>103</v>
       </c>
       <c r="AI28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ28" t="s">
         <v>103</v>
@@ -7142,16 +7115,16 @@
         <v>104</v>
       </c>
       <c r="BL28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BM28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BN28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BO28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BP28" t="s">
         <v>104</v>
@@ -7166,19 +7139,19 @@
         <v>104</v>
       </c>
       <c r="BT28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BU28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BV28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BW28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX28" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Beans_(fava,_dry)_tukey_classification_matrix.xlsx
+++ b/outputs/Beans_(fava,_dry)_tukey_classification_matrix.xlsx
@@ -325,7 +325,7 @@
     <t>Yambio</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
